--- a/Res_ConvLSTM/DroughtDataset_model_testing_1754918674_h_7.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1754918674_h_7.xlsx
@@ -658,7 +658,7 @@
         <v>0.008426604091929184</v>
       </c>
       <c r="C2" t="n">
-        <v>44424660</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>44424660</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>31990215</v>
+        <v>4199088</v>
       </c>
       <c r="L2" t="n">
-        <v>17791471</v>
+        <v>2056841</v>
       </c>
       <c r="M2" t="n">
-        <v>4168617</v>
+        <v>449902</v>
       </c>
       <c r="N2" t="n">
-        <v>155399</v>
+        <v>13771</v>
       </c>
       <c r="O2" t="n">
-        <v>2485605</v>
+        <v>274089</v>
       </c>
       <c r="P2" t="n">
-        <v>966597</v>
+        <v>112116</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9998531341552734</v>
+        <v>0.9998550415039062</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8787468075752258</v>
+        <v>0.7995031476020813</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7725874781608582</v>
+        <v>0.632979154586792</v>
       </c>
       <c r="T2" t="n">
-        <v>0.708827793598175</v>
+        <v>0.5333461165428162</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2168556898832321</v>
+        <v>0.1305592656135559</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7519814968109131</v>
+        <v>0.5952930450439453</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8441740274429321</v>
+        <v>0.7110936045646667</v>
       </c>
       <c r="X2" t="n">
-        <v>44424660</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>44424660</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>33898745</v>
+        <v>4822613</v>
       </c>
       <c r="AG2" t="n">
-        <v>20925813</v>
+        <v>3003787</v>
       </c>
       <c r="AH2" t="n">
-        <v>5610294</v>
+        <v>802859</v>
       </c>
       <c r="AI2" t="n">
-        <v>413892</v>
+        <v>59182</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3215996</v>
+        <v>460006</v>
       </c>
       <c r="AK2" t="n">
-        <v>1260508</v>
+        <v>180185</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9564294219017029</v>
+        <v>0.9558094143867493</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9113486409187317</v>
+        <v>0.9115616083145142</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8579833507537842</v>
+        <v>0.8578552603721619</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6620163917541504</v>
+        <v>0.6612218618392944</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019670486450195</v>
+        <v>0.9019814133644104</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.931441068649292</v>
+        <v>0.9314774870872498</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.00201955565764127</v>
       </c>
       <c r="C3" t="n">
-        <v>4868</v>
+        <v>699</v>
       </c>
       <c r="D3" t="n">
-        <v>31990215</v>
+        <v>4199088</v>
       </c>
       <c r="E3" t="n">
-        <v>3327011</v>
+        <v>807317</v>
       </c>
       <c r="F3" t="n">
-        <v>67547</v>
+        <v>25803</v>
       </c>
       <c r="G3" t="n">
-        <v>6846</v>
+        <v>2268</v>
       </c>
       <c r="H3" t="n">
-        <v>3932</v>
+        <v>1796</v>
       </c>
       <c r="I3" t="n">
-        <v>189</v>
+        <v>87</v>
       </c>
       <c r="J3" t="n">
-        <v>70480814</v>
+        <v>10068700</v>
       </c>
       <c r="K3" t="n">
-        <v>75097246</v>
+        <v>10325908</v>
       </c>
       <c r="L3" t="n">
-        <v>86678414</v>
+        <v>11921501</v>
       </c>
       <c r="M3" t="n">
-        <v>106656078</v>
+        <v>15085277</v>
       </c>
       <c r="N3" t="n">
-        <v>113725079</v>
+        <v>16234659</v>
       </c>
       <c r="O3" t="n">
-        <v>110524889</v>
+        <v>15719200</v>
       </c>
       <c r="P3" t="n">
-        <v>113380044</v>
+        <v>16176942</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9036628603935242</v>
+        <v>0.8336390256881714</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7736554145812988</v>
+        <v>0.6229304671287537</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6370585560798645</v>
+        <v>0.4801110625267029</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2483526915311813</v>
+        <v>0.153634175658226</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6967731118202209</v>
+        <v>0.5369430184364319</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7141293883323669</v>
+        <v>0.5793898701667786</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>33898745</v>
+        <v>4822613</v>
       </c>
       <c r="Z3" t="n">
-        <v>1393396</v>
+        <v>198886</v>
       </c>
       <c r="AA3" t="n">
-        <v>60111</v>
+        <v>8613</v>
       </c>
       <c r="AB3" t="n">
-        <v>47831</v>
+        <v>6871</v>
       </c>
       <c r="AC3" t="n">
-        <v>315</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>210</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>70487340</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>77967120</v>
+        <v>11155975</v>
       </c>
       <c r="AG3" t="n">
-        <v>89879810</v>
+        <v>12822698</v>
       </c>
       <c r="AH3" t="n">
-        <v>107439825</v>
+        <v>15345889</v>
       </c>
       <c r="AI3" t="n">
-        <v>114074974</v>
+        <v>16296043</v>
       </c>
       <c r="AJ3" t="n">
-        <v>110995151</v>
+        <v>15855549</v>
       </c>
       <c r="AK3" t="n">
-        <v>113465688</v>
+        <v>16209238</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575752019882202</v>
+        <v>0.9574265480041504</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099511504173279</v>
+        <v>0.9097204804420471</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8573793172836304</v>
+        <v>0.8567676544189453</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6614662408828735</v>
+        <v>0.660255491733551</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9015187621116638</v>
+        <v>0.9011561870574951</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312731623649597</v>
+        <v>0.9311549663543701</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.0318933357951476</v>
       </c>
       <c r="C4" t="n">
-        <v>383</v>
+        <v>74</v>
       </c>
       <c r="D4" t="n">
-        <v>4144950</v>
+        <v>984121</v>
       </c>
       <c r="E4" t="n">
-        <v>17791471</v>
+        <v>2056841</v>
       </c>
       <c r="F4" t="n">
-        <v>938180</v>
+        <v>218039</v>
       </c>
       <c r="G4" t="n">
-        <v>43155</v>
+        <v>13562</v>
       </c>
       <c r="H4" t="n">
-        <v>72052</v>
+        <v>26459</v>
       </c>
       <c r="I4" t="n">
-        <v>6443</v>
+        <v>2783</v>
       </c>
       <c r="J4" t="n">
-        <v>6526</v>
+        <v>920</v>
       </c>
       <c r="K4" t="n">
-        <v>4414146</v>
+        <v>1053034</v>
       </c>
       <c r="L4" t="n">
-        <v>5236952</v>
+        <v>1192620</v>
       </c>
       <c r="M4" t="n">
-        <v>1712384</v>
+        <v>393644</v>
       </c>
       <c r="N4" t="n">
-        <v>561202</v>
+        <v>91706</v>
       </c>
       <c r="O4" t="n">
-        <v>819802</v>
+        <v>186338</v>
       </c>
       <c r="P4" t="n">
-        <v>178424</v>
+        <v>45551</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999265670776367</v>
+        <v>0.9999275207519531</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8910307288169861</v>
+        <v>0.8162143230438232</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7731210589408875</v>
+        <v>0.6279146075248718</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6710296273231506</v>
+        <v>0.5053304433822632</v>
       </c>
       <c r="U4" t="n">
-        <v>0.231537938117981</v>
+        <v>0.1411599367856979</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7233253717422485</v>
+        <v>0.564614474773407</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7737254500389099</v>
+        <v>0.6385210156440735</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1441845</v>
+        <v>208181</v>
       </c>
       <c r="Z4" t="n">
-        <v>20925813</v>
+        <v>3003787</v>
       </c>
       <c r="AA4" t="n">
-        <v>581832</v>
+        <v>83142</v>
       </c>
       <c r="AB4" t="n">
-        <v>38644</v>
+        <v>5553</v>
       </c>
       <c r="AC4" t="n">
-        <v>8024</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>476</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1544272</v>
+        <v>222967</v>
       </c>
       <c r="AG4" t="n">
-        <v>2035556</v>
+        <v>291423</v>
       </c>
       <c r="AH4" t="n">
-        <v>928637</v>
+        <v>133032</v>
       </c>
       <c r="AI4" t="n">
-        <v>211307</v>
+        <v>30322</v>
       </c>
       <c r="AJ4" t="n">
-        <v>349540</v>
+        <v>49989</v>
       </c>
       <c r="AK4" t="n">
-        <v>92780</v>
+        <v>13255</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9570019841194153</v>
+        <v>0.9566173553466797</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106493592262268</v>
+        <v>0.9106400609016418</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8576812148094177</v>
+        <v>0.8573110699653625</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6617411971092224</v>
+        <v>0.6607382893562317</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017428159713745</v>
+        <v>0.9015686511993408</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313570857048035</v>
+        <v>0.9313161373138428</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>180107</v>
+        <v>49266</v>
       </c>
       <c r="E5" t="n">
-        <v>1642351</v>
+        <v>315393</v>
       </c>
       <c r="F5" t="n">
-        <v>4168617</v>
+        <v>449902</v>
       </c>
       <c r="G5" t="n">
-        <v>188717</v>
+        <v>29781</v>
       </c>
       <c r="H5" t="n">
-        <v>333594</v>
+        <v>82230</v>
       </c>
       <c r="I5" t="n">
-        <v>30049</v>
+        <v>10494</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>3410393</v>
+        <v>837970</v>
       </c>
       <c r="L5" t="n">
-        <v>5205163</v>
+        <v>1245038</v>
       </c>
       <c r="M5" t="n">
-        <v>2374921</v>
+        <v>487177</v>
       </c>
       <c r="N5" t="n">
-        <v>470320</v>
+        <v>75864</v>
       </c>
       <c r="O5" t="n">
-        <v>1081704</v>
+        <v>236373</v>
       </c>
       <c r="P5" t="n">
-        <v>386935</v>
+        <v>81391</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999431967735291</v>
+        <v>0.9999439716339111</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9319084286689758</v>
+        <v>0.884807288646698</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9091294407844543</v>
+        <v>0.8515071868896484</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9644309878349304</v>
+        <v>0.9463437795639038</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9910233616828918</v>
+        <v>0.9897922873497009</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9834524989128113</v>
+        <v>0.9742500782012939</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9950800538063049</v>
+        <v>0.9922671914100647</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>56517</v>
+        <v>8150</v>
       </c>
       <c r="Z5" t="n">
-        <v>598295</v>
+        <v>86254</v>
       </c>
       <c r="AA5" t="n">
-        <v>5610294</v>
+        <v>802859</v>
       </c>
       <c r="AB5" t="n">
-        <v>69798</v>
+        <v>9996</v>
       </c>
       <c r="AC5" t="n">
-        <v>204203</v>
+        <v>29187</v>
       </c>
       <c r="AD5" t="n">
-        <v>4431</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1501863</v>
+        <v>214445</v>
       </c>
       <c r="AG5" t="n">
-        <v>2070821</v>
+        <v>298092</v>
       </c>
       <c r="AH5" t="n">
-        <v>933244</v>
+        <v>134220</v>
       </c>
       <c r="AI5" t="n">
-        <v>211827</v>
+        <v>30453</v>
       </c>
       <c r="AJ5" t="n">
-        <v>351313</v>
+        <v>50456</v>
       </c>
       <c r="AK5" t="n">
-        <v>93024</v>
+        <v>13322</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734916090965271</v>
+        <v>0.9733545184135437</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9642650485038757</v>
+        <v>0.9640889763832092</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837973117828369</v>
+        <v>0.9837200045585632</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963177442550659</v>
+        <v>0.9962978363037109</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9939009547233582</v>
+        <v>0.9938812851905823</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.998383104801178</v>
+        <v>0.9983810186386108</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>307</v>
+        <v>43</v>
       </c>
       <c r="D6" t="n">
-        <v>84099</v>
+        <v>16611</v>
       </c>
       <c r="E6" t="n">
-        <v>137067</v>
+        <v>21408</v>
       </c>
       <c r="F6" t="n">
-        <v>173681</v>
+        <v>25610</v>
       </c>
       <c r="G6" t="n">
-        <v>155399</v>
+        <v>13771</v>
       </c>
       <c r="H6" t="n">
-        <v>70020</v>
+        <v>10808</v>
       </c>
       <c r="I6" t="n">
-        <v>5146</v>
+        <v>1384</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>45519</v>
+        <v>6580</v>
       </c>
       <c r="Z6" t="n">
-        <v>37622</v>
+        <v>5392</v>
       </c>
       <c r="AA6" t="n">
-        <v>76408</v>
+        <v>11005</v>
       </c>
       <c r="AB6" t="n">
-        <v>413892</v>
+        <v>59182</v>
       </c>
       <c r="AC6" t="n">
-        <v>48911</v>
+        <v>6995</v>
       </c>
       <c r="AD6" t="n">
-        <v>3367</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>135</v>
+        <v>16</v>
       </c>
       <c r="D7" t="n">
-        <v>4749</v>
+        <v>2965</v>
       </c>
       <c r="E7" t="n">
-        <v>122554</v>
+        <v>44813</v>
       </c>
       <c r="F7" t="n">
-        <v>509164</v>
+        <v>115600</v>
       </c>
       <c r="G7" t="n">
-        <v>308505</v>
+        <v>42176</v>
       </c>
       <c r="H7" t="n">
-        <v>2485605</v>
+        <v>274089</v>
       </c>
       <c r="I7" t="n">
-        <v>136597</v>
+        <v>30803</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>195</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>5676</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>207971</v>
+        <v>29939</v>
       </c>
       <c r="AB7" t="n">
-        <v>53175</v>
+        <v>7636</v>
       </c>
       <c r="AC7" t="n">
-        <v>3215996</v>
+        <v>460006</v>
       </c>
       <c r="AD7" t="n">
-        <v>84296</v>
+        <v>12043</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>730</v>
+        <v>75</v>
       </c>
       <c r="D8" t="n">
-        <v>241</v>
+        <v>71</v>
       </c>
       <c r="E8" t="n">
-        <v>7969</v>
+        <v>3689</v>
       </c>
       <c r="F8" t="n">
-        <v>23812</v>
+        <v>8592</v>
       </c>
       <c r="G8" t="n">
-        <v>13979</v>
+        <v>3919</v>
       </c>
       <c r="H8" t="n">
-        <v>340204</v>
+        <v>65045</v>
       </c>
       <c r="I8" t="n">
-        <v>966597</v>
+        <v>112116</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>196</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>567</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>2315</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>1859</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>88087</v>
+        <v>12614</v>
       </c>
       <c r="AD8" t="n">
-        <v>1260508</v>
+        <v>180185</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
